--- a/test/generated_test_questions.xlsx
+++ b/test/generated_test_questions.xlsx
@@ -490,11 +490,37 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t># JOGI SZAKVÉLEMÉNY: A munkaszerződés írásba foglalási kötelezettsége és az elmaradás jogkövetkezményei
+### RÖVID VÁLASZ
+Igen, a munkáltató köteles a munkaszerződést írásba foglalni. A munkaszerződés írásba foglalásának elmulasztása esetén az érvénytelenségre kizárólag a munkavállaló hivatkozhat, a munkába lépést követő harminc napon belül.
+### JOGI INDOKOLÁS
+A 2012. évi I. törvény a munka törvénykönyvéről (Mt.) 44. §-a értelmében a munkaszerződést írásba kell foglalni, amelynek elvégzéséért a munkáltató köteles gondoskodni. Ez a rendelkezés garanciális szabály a munkavállaló védelme érdekében.
+A jogszabály kifejezetten meghatározza az írásba foglalás elmaradásának jogkövetkezményét: amennyiben a munkáltató ezen kötelezettségét elmulasztja, az érvénytelenség jogkövetkezményére csak a munkavállaló hivatkozhat, mégpedig a munkába lépést követő harminc napon belül. Ezen határidő jogvesztő jellegű, azaz a 30 nap elteltét követően a munkavállaló ezen az alapon a szerződés érvénytelenségére már nem hivatkozhat.
+Az érvénytelen munkaszerződés alapján történő munkavégzéssel kapcsolatban az Mt. rögzíti, hogy a munkavállalót munkabér illeti meg, biztosítva ezzel a ténylegesen elvégzett munkáért járó javadalmazást. A munkavállaló követelését az érvénytelenség megállapítását követően a polgári jogi szabályok szerint érvényesítheti.
+Ezen túlmenően a munkáltatót a munkaviszony kapcsán adatkezelési tájékoztatási kötelezettség is terheli. Az Európai Parlament és a Tanács (EU) 2016/679 rendelete (GDPR) 13. cikke alapján a munkáltató köteles a munkavállalót a munkaszerződés megkötését megelőzően tájékoztatni az adatkezelés céljáról, jogalapjáról, valamint az adatkezelés időtartamáról. A tájékoztatásnak ki kell terjednie a munkavállaló adatkezeléssel összefüggő jogaira is.
+### JOGSZABÁLYI HIVATKOZÁSOK
+- 2012. évi I. törvény a munka törvénykönyvéről: 44. §
+- Az Európai Parlament és a Tanács (EU) 2016/679 rendelete (GDPR): 13. cikk
+### KOCKÁZATI TÉNYEZŐK ÉS KIVÉTELEK
+A munkaszerződés írásba foglalásának elmulasztása a munkáltató részéről súlyos mulasztásnak minősül, amely jogi bizonytalanságot és a munkavállalói igényérvényesítés kockázatát hordozza magában a 30 napos szubjektív határidőn belül. Fontos rögzíteni, hogy a munkáltató saját mulasztására hivatkozással nem kezdeményezheti a szerződés érvénytelenségének megállapítását, mivel a törvényi védelem kifejezetten a munkavállalót illeti meg. A 30 napos határidőn túli jogérvényesítés a munkaszerződés írásbeli hiányossága miatt már nem lehetséges.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The score is 1.00 because the actual output is completely faithful to the provided retrieval context with no contradictions found. Excellent work maintaining accuracy!</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,11 +544,38 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t># JOGI SZAKVÉLEMÉNY: 22 éves munkavállaló éves szabadságának mértéke
+### RÖVID VÁLASZ
+Egy 22 éves munkavállalónak – amennyiben munkaviszonya a teljes naptári évre kiterjed – évente összesen 21 munkanap szabadság jár.
+### JOGI INDOKOLÁS
+A munkavállalót megillető szabadság mértéke a 2012. évi I. törvény (a munka törvénykönyve, a továbbiakban: Mt.) rendelkezései alapján az alapszabadságból és az életkor szerinti pótszabadságból tevődik össze.
+1. Alapszabadság: Az Mt. 116. § (1) bekezdése értelmében a munkavállalónak minden naptári évben 20 munkanap alapszabadság jár. A 22 éves munkavállaló alanyi jogon jogosult erre az időtartamra.
+2. Életkor szerinti pótszabadság: Az Mt. 117. § (1) bekezdése kimondja: „A munkavállalónak a tizennyolcadik életévének betöltése évétől kezdődően évenként egy munkanap pótszabadság jár.” Mivel a munkavállaló a 22. életévét betöltötte, az életkora alapján jogosult az évenkénti egy munkanap pótszabadságra.
+3. Összesítés: A két jogcímen járó szabadságnapok összege: 20 munkanap alapszabadság + 1 munkanap pótszabadság = 21 munkanap.
+### JOGSZABÁLYI HIVATKOZÁSOK
+- 2012. évi I. törvény a munka törvénykönyvéről 116. § (1) bekezdés
+- 2012. évi I. törvény a munka törvénykönyvéről 117. § (1) bekezdés
+- 2012. évi I. törvény a munka törvénykönyvéről 122. § (1) bekezdés
+### KOCKÁZATI TÉNYEZŐK ÉS KIVÉTELEK
+A 21 munkanapos szabadság mértéke kizárólag a teljes naptári évre fennálló munkaviszony esetén irányadó. Amennyiben a munkaviszony év közben kezdődött vagy szűnt meg, a szabadságot az arányosítás szabályai szerint kell kiadni. Az arányosítás elmulasztása jogszabálysértő, és munkaügyi kockázatot keletkeztet a munkáltató oldalán. Az arányosítási kötelezettséget az Mt. 122. § (1) bekezdése írja elő.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The score is 1.00 because the actual output is perfectly aligned with the retrieval context, showing no contradictions at all! Great job on maintaining such high accuracy!</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
